--- a/UTCUTS/A1_Outputs/reference_freeze/A-O_Fleet.xlsx
+++ b/UTCUTS/A1_Outputs/reference_freeze/A-O_Fleet.xlsx
@@ -931,7 +931,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0651C60-6F2A-4548-A04B-03C5B40FB8F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9742D865-44EF-436A-A0DF-5AEF6A2412C0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
